--- a/clientportal/Raw Data - 4864_OC-CR.xlsx
+++ b/clientportal/Raw Data - 4864_OC-CR.xlsx
@@ -1580,6 +1580,27 @@
     <t>Proceso en Curso</t>
   </si>
   <si>
+    <t>CR-L1139-P00075</t>
+  </si>
+  <si>
+    <t>Contratación de Ingeniero de apoyo para el Programa PIV APP </t>
+  </si>
+  <si>
+    <t>Servicios de consultor individual para apoyar en el periodo de notificación de defectos y cierre del contrato de Obra para los Intercambios de Taras y la Lima </t>
+  </si>
+  <si>
+    <t>Borrador</t>
+  </si>
+  <si>
+    <t>CR-L1139-P00076</t>
+  </si>
+  <si>
+    <t>Contratación de consultor que  apoye a la oficina de la OGAS para el Programa PIV APP </t>
+  </si>
+  <si>
+    <t>Servicios de consultor individual para apoyar el trabajo de la oficina de la OGAS en los Intercambios de San José a San Ramón</t>
+  </si>
+  <si>
     <t>Publicación del AEA</t>
   </si>
   <si>
@@ -1730,24 +1751,24 @@
     <t>Consorcio TYPSA-C&amp;DLT</t>
   </si>
   <si>
+    <t>Castro &amp; De la Torre</t>
+  </si>
+  <si>
     <t>TÉCNICA Y PROYECTOS S.A. (TYPSA)</t>
   </si>
   <si>
-    <t>Castro &amp; De la Torre</t>
-  </si>
-  <si>
     <t>Consorcio PEYCO-ATJ-SEG</t>
   </si>
   <si>
     <t>Asistencia Técnica y Jurídica Consultores S.L.</t>
   </si>
   <si>
+    <t>SONDEOS, ESTRUCTURAS Y GEOTECNIA</t>
+  </si>
+  <si>
     <t>Proyectos, Estudios y Construcciones, S.A. (PEYCO)</t>
   </si>
   <si>
-    <t>SONDEOS, ESTRUCTURAS Y GEOTECNIA</t>
-  </si>
-  <si>
     <t>AC &amp; A</t>
   </si>
   <si>
@@ -1757,13 +1778,13 @@
     <t>Consorcio Supervisor 4 intercambios (CACISA E INSERINSA)</t>
   </si>
   <si>
+    <t>Ingenieria, Servicios e Inversiones S.A. de C.V. INSERINSA</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
     <t>CACISA S.A.</t>
-  </si>
-  <si>
-    <t>Ingenieria, Servicios e Inversiones S.A. de C.V. INSERINSA</t>
-  </si>
-  <si>
-    <t>El Salvador</t>
   </si>
   <si>
     <t>Consorcio VIELCA-PINI</t>
@@ -2599,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z74"/>
+  <dimension ref="A1:Z76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="25.6640625" customWidth="1"/>
@@ -7260,6 +7281,130 @@
       <c r="Y74"/>
       <c r="Z74" t="s">
         <v>429</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>230</v>
+      </c>
+      <c r="B75" t="s">
+        <v>511</v>
+      </c>
+      <c r="C75" t="s">
+        <v>232</v>
+      </c>
+      <c r="D75" t="s">
+        <v>512</v>
+      </c>
+      <c r="E75" t="s">
+        <v>513</v>
+      </c>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75" t="s">
+        <v>246</v>
+      </c>
+      <c r="I75" t="s">
+        <v>477</v>
+      </c>
+      <c r="J75" t="s">
+        <v>237</v>
+      </c>
+      <c r="K75" t="n" s="3">
+        <v>55000</v>
+      </c>
+      <c r="L75" s="3"/>
+      <c r="M75" t="n">
+        <v>100</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>239</v>
+      </c>
+      <c r="R75" t="s">
+        <v>240</v>
+      </c>
+      <c r="S75" t="s">
+        <v>514</v>
+      </c>
+      <c r="T75"/>
+      <c r="U75"/>
+      <c r="V75"/>
+      <c r="W75"/>
+      <c r="X75"/>
+      <c r="Y75"/>
+      <c r="Z75" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>230</v>
+      </c>
+      <c r="B76" t="s">
+        <v>515</v>
+      </c>
+      <c r="C76" t="s">
+        <v>232</v>
+      </c>
+      <c r="D76" t="s">
+        <v>516</v>
+      </c>
+      <c r="E76" t="s">
+        <v>517</v>
+      </c>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76" t="s">
+        <v>246</v>
+      </c>
+      <c r="I76" t="s">
+        <v>247</v>
+      </c>
+      <c r="J76" t="s">
+        <v>237</v>
+      </c>
+      <c r="K76" t="n" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L76" s="3"/>
+      <c r="M76" t="n">
+        <v>100</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>239</v>
+      </c>
+      <c r="R76" t="s">
+        <v>430</v>
+      </c>
+      <c r="S76" t="s">
+        <v>514</v>
+      </c>
+      <c r="T76"/>
+      <c r="U76"/>
+      <c r="V76"/>
+      <c r="W76"/>
+      <c r="X76"/>
+      <c r="Y76"/>
+      <c r="Z76" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -7296,36 +7441,36 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="C2" t="n" s="5">
         <v>45751</v>
       </c>
       <c r="D2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B3" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>45751</v>
       </c>
       <c r="D3" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="E3" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -7339,27 +7484,27 @@
         <v>45776</v>
       </c>
       <c r="D4" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="E4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B5" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>45751</v>
       </c>
       <c r="D5" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E5" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7373,10 +7518,10 @@
         <v>45803</v>
       </c>
       <c r="D6" t="s">
+        <v>720</v>
+      </c>
+      <c r="E6" t="s">
         <v>713</v>
-      </c>
-      <c r="E6" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7390,10 +7535,10 @@
         <v>45819</v>
       </c>
       <c r="D7" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="E7" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -7407,10 +7552,10 @@
         <v>45877</v>
       </c>
       <c r="D8" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="E8" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -7424,10 +7569,10 @@
         <v>45751</v>
       </c>
       <c r="D9" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E9" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -7441,10 +7586,10 @@
         <v>45877</v>
       </c>
       <c r="D10" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="E10" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -7458,10 +7603,10 @@
         <v>45877</v>
       </c>
       <c r="D11" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="E11" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -7475,10 +7620,10 @@
         <v>45812</v>
       </c>
       <c r="D12" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="E12" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -7492,10 +7637,10 @@
         <v>45845</v>
       </c>
       <c r="D13" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E13" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -7509,10 +7654,10 @@
         <v>45845</v>
       </c>
       <c r="D14" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E14" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -7526,10 +7671,10 @@
         <v>45845</v>
       </c>
       <c r="D15" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E15" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -7543,61 +7688,61 @@
         <v>45917</v>
       </c>
       <c r="D16" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E16" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B17" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>46003</v>
       </c>
       <c r="D17" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B18" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="C18" t="n" s="5">
         <v>45959</v>
       </c>
       <c r="D18" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="E18" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B19" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>46034</v>
       </c>
       <c r="D19" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="E19" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -7611,15 +7756,15 @@
         <v>46003</v>
       </c>
       <c r="D20" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="E20" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B21" t="s">
         <v>476</v>
@@ -7628,15 +7773,15 @@
         <v>46003</v>
       </c>
       <c r="D21" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="E21" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B22" t="s">
         <v>476</v>
@@ -7645,15 +7790,15 @@
         <v>45917</v>
       </c>
       <c r="D22" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E22" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B23" t="s">
         <v>476</v>
@@ -7662,15 +7807,15 @@
         <v>46121</v>
       </c>
       <c r="D23" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="E23" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B24" t="s">
         <v>481</v>
@@ -7679,15 +7824,15 @@
         <v>45917</v>
       </c>
       <c r="D24" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E24" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B25" t="s">
         <v>481</v>
@@ -7696,15 +7841,15 @@
         <v>46121</v>
       </c>
       <c r="D25" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="E25" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B26" t="s">
         <v>481</v>
@@ -7713,10 +7858,10 @@
         <v>46003</v>
       </c>
       <c r="D26" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E26" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -7730,10 +7875,10 @@
         <v>46142</v>
       </c>
       <c r="D27" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="E27" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -7747,10 +7892,10 @@
         <v>45972</v>
       </c>
       <c r="D28" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="E28" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>
@@ -7760,7 +7905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA70B816-A7E8-478F-96D4-061C9871C9B8}">
-  <dimension ref="A1:K244"/>
+  <dimension ref="A1:K250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
@@ -7823,7 +7968,7 @@
         <v>237</v>
       </c>
       <c r="F2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G2" t="n" s="5">
         <v>43563</v>
@@ -7852,7 +7997,7 @@
         <v>237</v>
       </c>
       <c r="F3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G3" t="n" s="5">
         <v>43691</v>
@@ -7881,7 +8026,7 @@
         <v>237</v>
       </c>
       <c r="F4" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="G4" t="n" s="5">
         <v>43803</v>
@@ -7910,7 +8055,7 @@
         <v>237</v>
       </c>
       <c r="F5" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G5" t="n" s="5">
         <v>44078</v>
@@ -7939,7 +8084,7 @@
         <v>237</v>
       </c>
       <c r="F6" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G6" t="n" s="5">
         <v>44088</v>
@@ -7968,7 +8113,7 @@
         <v>237</v>
       </c>
       <c r="F7" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G7" t="n" s="5">
         <v>44550</v>
@@ -7997,7 +8142,7 @@
         <v>237</v>
       </c>
       <c r="F8" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G8" t="n" s="5">
         <v>44590</v>
@@ -8026,7 +8171,7 @@
         <v>237</v>
       </c>
       <c r="F9" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G9" t="n" s="5">
         <v>44600</v>
@@ -8055,7 +8200,7 @@
         <v>237</v>
       </c>
       <c r="F10" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G10" t="n" s="5">
         <v>44620</v>
@@ -8084,7 +8229,7 @@
         <v>237</v>
       </c>
       <c r="F11" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G11" t="n" s="5">
         <v>44676</v>
@@ -8113,7 +8258,7 @@
         <v>237</v>
       </c>
       <c r="F12" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G12" t="n" s="5">
         <v>44676</v>
@@ -8142,7 +8287,7 @@
         <v>237</v>
       </c>
       <c r="F13" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G13" t="n" s="5">
         <v>44624</v>
@@ -8171,7 +8316,7 @@
         <v>237</v>
       </c>
       <c r="F14" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G14" t="n" s="5">
         <v>44628</v>
@@ -8200,7 +8345,7 @@
         <v>237</v>
       </c>
       <c r="F15" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G15" t="n" s="5">
         <v>44638</v>
@@ -8229,7 +8374,7 @@
         <v>237</v>
       </c>
       <c r="F16" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G16" t="n" s="5">
         <v>44634</v>
@@ -8258,7 +8403,7 @@
         <v>237</v>
       </c>
       <c r="F17" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G17" t="n" s="5">
         <v>44675</v>
@@ -8287,7 +8432,7 @@
         <v>237</v>
       </c>
       <c r="F18" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G18" t="n" s="5">
         <v>44685</v>
@@ -8316,7 +8461,7 @@
         <v>237</v>
       </c>
       <c r="F19" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G19" t="n" s="5">
         <v>44463</v>
@@ -8345,7 +8490,7 @@
         <v>237</v>
       </c>
       <c r="F20" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G20" t="n" s="5">
         <v>44460</v>
@@ -8374,7 +8519,7 @@
         <v>237</v>
       </c>
       <c r="F21" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G21" t="n" s="5">
         <v>44470</v>
@@ -8403,7 +8548,7 @@
         <v>237</v>
       </c>
       <c r="F22" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G22" t="n" s="5">
         <v>43606</v>
@@ -8432,7 +8577,7 @@
         <v>237</v>
       </c>
       <c r="F23" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G23" t="n" s="5">
         <v>43668</v>
@@ -8461,7 +8606,7 @@
         <v>237</v>
       </c>
       <c r="F24" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G24" t="n" s="5">
         <v>43714</v>
@@ -8490,7 +8635,7 @@
         <v>237</v>
       </c>
       <c r="F25" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G25" t="n" s="5">
         <v>43844</v>
@@ -8519,7 +8664,7 @@
         <v>237</v>
       </c>
       <c r="F26" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G26" t="n" s="5">
         <v>43845</v>
@@ -8548,7 +8693,7 @@
         <v>237</v>
       </c>
       <c r="F27" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G27" t="n" s="5">
         <v>43846</v>
@@ -8577,7 +8722,7 @@
         <v>237</v>
       </c>
       <c r="F28" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G28" t="n" s="5">
         <v>43847</v>
@@ -8606,7 +8751,7 @@
         <v>237</v>
       </c>
       <c r="F29" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G29" t="n" s="5">
         <v>44081</v>
@@ -8635,7 +8780,7 @@
         <v>237</v>
       </c>
       <c r="F30" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G30" t="n" s="5">
         <v>44470</v>
@@ -8664,7 +8809,7 @@
         <v>237</v>
       </c>
       <c r="F31" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G31" t="n" s="5">
         <v>44484</v>
@@ -8693,7 +8838,7 @@
         <v>237</v>
       </c>
       <c r="F32" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G32" t="n" s="5">
         <v>44498</v>
@@ -8722,7 +8867,7 @@
         <v>237</v>
       </c>
       <c r="F33" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G33" t="n" s="5">
         <v>44499</v>
@@ -8751,7 +8896,7 @@
         <v>237</v>
       </c>
       <c r="F34" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G34" t="n" s="5">
         <v>44624</v>
@@ -8780,7 +8925,7 @@
         <v>237</v>
       </c>
       <c r="F35" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G35" t="n" s="5">
         <v>44638</v>
@@ -8809,7 +8954,7 @@
         <v>237</v>
       </c>
       <c r="F36" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G36" t="n" s="5">
         <v>44634</v>
@@ -8838,7 +8983,7 @@
         <v>237</v>
       </c>
       <c r="F37" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G37" t="n" s="5">
         <v>44684</v>
@@ -8867,7 +9012,7 @@
         <v>237</v>
       </c>
       <c r="F38" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G38" t="n" s="5">
         <v>44684</v>
@@ -8896,7 +9041,7 @@
         <v>237</v>
       </c>
       <c r="F39" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G39" t="n" s="5">
         <v>44573</v>
@@ -8925,7 +9070,7 @@
         <v>237</v>
       </c>
       <c r="F40" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G40" t="n" s="5">
         <v>44583</v>
@@ -8954,7 +9099,7 @@
         <v>237</v>
       </c>
       <c r="F41" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G41" t="n" s="5">
         <v>44593</v>
@@ -8983,7 +9128,7 @@
         <v>237</v>
       </c>
       <c r="F42" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G42" t="n" s="5">
         <v>44624</v>
@@ -9012,7 +9157,7 @@
         <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G43" t="n" s="5">
         <v>44803</v>
@@ -9041,7 +9186,7 @@
         <v>237</v>
       </c>
       <c r="F44" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G44" t="n" s="5">
         <v>44803</v>
@@ -9070,7 +9215,7 @@
         <v>237</v>
       </c>
       <c r="F45" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G45" t="n" s="5">
         <v>44141</v>
@@ -9099,7 +9244,7 @@
         <v>237</v>
       </c>
       <c r="F46" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G46" t="n" s="5">
         <v>44368</v>
@@ -9128,7 +9273,7 @@
         <v>237</v>
       </c>
       <c r="F47" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G47" t="n" s="5">
         <v>44389</v>
@@ -9157,7 +9302,7 @@
         <v>237</v>
       </c>
       <c r="F48" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G48" t="n" s="5">
         <v>44463</v>
@@ -9186,7 +9331,7 @@
         <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G49" t="n" s="5">
         <v>44530</v>
@@ -9215,7 +9360,7 @@
         <v>237</v>
       </c>
       <c r="F50" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G50" t="n" s="5">
         <v>44540</v>
@@ -9244,7 +9389,7 @@
         <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G51" t="n" s="5">
         <v>44560</v>
@@ -9273,7 +9418,7 @@
         <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G52" t="n" s="5">
         <v>44597</v>
@@ -9302,7 +9447,7 @@
         <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G53" t="n" s="5">
         <v>44607</v>
@@ -9331,7 +9476,7 @@
         <v>237</v>
       </c>
       <c r="F54" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G54" t="n" s="5">
         <v>44522</v>
@@ -9360,7 +9505,7 @@
         <v>237</v>
       </c>
       <c r="F55" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G55" t="n" s="5">
         <v>44582</v>
@@ -9389,7 +9534,7 @@
         <v>237</v>
       </c>
       <c r="F56" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G56" t="n" s="5">
         <v>44592</v>
@@ -9418,7 +9563,7 @@
         <v>237</v>
       </c>
       <c r="F57" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G57" t="n" s="5">
         <v>44911</v>
@@ -9447,7 +9592,7 @@
         <v>237</v>
       </c>
       <c r="F58" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G58" t="n" s="5">
         <v>44939</v>
@@ -9476,7 +9621,7 @@
         <v>237</v>
       </c>
       <c r="F59" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G59" t="n" s="5">
         <v>44939</v>
@@ -9505,7 +9650,7 @@
         <v>237</v>
       </c>
       <c r="F60" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G60" t="n" s="5">
         <v>45351</v>
@@ -9534,7 +9679,7 @@
         <v>237</v>
       </c>
       <c r="F61" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G61" t="n" s="5">
         <v>45382</v>
@@ -9563,7 +9708,7 @@
         <v>237</v>
       </c>
       <c r="F62" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G62" t="n" s="5">
         <v>45382</v>
@@ -9592,7 +9737,7 @@
         <v>237</v>
       </c>
       <c r="F63" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G63" t="n" s="5">
         <v>45044</v>
@@ -9621,7 +9766,7 @@
         <v>237</v>
       </c>
       <c r="F64" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G64" t="n" s="5">
         <v>45100</v>
@@ -9650,7 +9795,7 @@
         <v>237</v>
       </c>
       <c r="F65" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G65" t="n" s="5">
         <v>45114</v>
@@ -9679,7 +9824,7 @@
         <v>237</v>
       </c>
       <c r="F66" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G66" t="n" s="5">
         <v>44439</v>
@@ -9708,7 +9853,7 @@
         <v>237</v>
       </c>
       <c r="F67" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G67" t="n" s="5">
         <v>44547</v>
@@ -9737,7 +9882,7 @@
         <v>237</v>
       </c>
       <c r="F68" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="G68" t="n" s="5">
         <v>44607</v>
@@ -9766,7 +9911,7 @@
         <v>237</v>
       </c>
       <c r="F69" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G69" t="n" s="5">
         <v>44803</v>
@@ -9795,7 +9940,7 @@
         <v>237</v>
       </c>
       <c r="F70" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G70" t="n" s="5">
         <v>44813</v>
@@ -9824,7 +9969,7 @@
         <v>237</v>
       </c>
       <c r="F71" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G71" t="n" s="5">
         <v>45044</v>
@@ -9853,7 +9998,7 @@
         <v>237</v>
       </c>
       <c r="F72" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G72" t="n" s="5">
         <v>45107</v>
@@ -9882,7 +10027,7 @@
         <v>237</v>
       </c>
       <c r="F73" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G73" t="n" s="5">
         <v>45138</v>
@@ -9911,7 +10056,7 @@
         <v>237</v>
       </c>
       <c r="F74" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G74" t="n" s="5">
         <v>45107</v>
@@ -9940,7 +10085,7 @@
         <v>237</v>
       </c>
       <c r="F75" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G75" t="n" s="5">
         <v>45104</v>
@@ -9969,7 +10114,7 @@
         <v>237</v>
       </c>
       <c r="F76" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G76" t="n" s="5">
         <v>45114</v>
@@ -9998,7 +10143,7 @@
         <v>237</v>
       </c>
       <c r="F77" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G77" t="n" s="5">
         <v>45107</v>
@@ -10027,7 +10172,7 @@
         <v>237</v>
       </c>
       <c r="F78" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G78" t="n" s="5">
         <v>45104</v>
@@ -10056,7 +10201,7 @@
         <v>237</v>
       </c>
       <c r="F79" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G79" t="n" s="5">
         <v>45114</v>
@@ -10085,7 +10230,7 @@
         <v>237</v>
       </c>
       <c r="F80" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G80" t="n" s="5">
         <v>45163</v>
@@ -10114,7 +10259,7 @@
         <v>237</v>
       </c>
       <c r="F81" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G81" t="n" s="5">
         <v>45190</v>
@@ -10143,7 +10288,7 @@
         <v>237</v>
       </c>
       <c r="F82" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G82" t="n" s="5">
         <v>45226</v>
@@ -10172,7 +10317,7 @@
         <v>237</v>
       </c>
       <c r="F83" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G83" t="n" s="5">
         <v>45351</v>
@@ -10201,7 +10346,7 @@
         <v>237</v>
       </c>
       <c r="F84" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G84" t="n" s="5">
         <v>45352</v>
@@ -10230,7 +10375,7 @@
         <v>237</v>
       </c>
       <c r="F85" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G85" t="n" s="5">
         <v>45565</v>
@@ -10259,7 +10404,7 @@
         <v>237</v>
       </c>
       <c r="F86" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G86" t="n" s="5">
         <v>45566</v>
@@ -10288,7 +10433,7 @@
         <v>237</v>
       </c>
       <c r="F87" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G87" t="n" s="5">
         <v>45688</v>
@@ -10317,7 +10462,7 @@
         <v>237</v>
       </c>
       <c r="F88" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="G88" t="n" s="5">
         <v>45345</v>
@@ -10346,7 +10491,7 @@
         <v>237</v>
       </c>
       <c r="F89" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G89" t="n" s="5">
         <v>45401</v>
@@ -10375,7 +10520,7 @@
         <v>237</v>
       </c>
       <c r="F90" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G90" t="n" s="5">
         <v>45138</v>
@@ -10404,7 +10549,7 @@
         <v>237</v>
       </c>
       <c r="F91" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G91" t="n" s="5">
         <v>45146</v>
@@ -10433,7 +10578,7 @@
         <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G92" t="n" s="5">
         <v>45156</v>
@@ -10462,7 +10607,7 @@
         <v>237</v>
       </c>
       <c r="F93" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G93" t="n" s="5">
         <v>44362</v>
@@ -10491,7 +10636,7 @@
         <v>237</v>
       </c>
       <c r="F94" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G94" t="n" s="5">
         <v>44434</v>
@@ -10520,7 +10665,7 @@
         <v>237</v>
       </c>
       <c r="F95" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G95" t="n" s="5">
         <v>44533</v>
@@ -10549,7 +10694,7 @@
         <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G96" t="n" s="5">
         <v>44649</v>
@@ -10578,7 +10723,7 @@
         <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G97" t="n" s="5">
         <v>44650</v>
@@ -10607,7 +10752,7 @@
         <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G98" t="n" s="5">
         <v>44810</v>
@@ -10636,7 +10781,7 @@
         <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G99" t="n" s="5">
         <v>44811</v>
@@ -10665,7 +10810,7 @@
         <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G100" t="n" s="5">
         <v>45154</v>
@@ -10694,7 +10839,7 @@
         <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G101" t="n" s="5">
         <v>45212</v>
@@ -10723,7 +10868,7 @@
         <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G102" t="n" s="5">
         <v>45216</v>
@@ -10752,7 +10897,7 @@
         <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G103" t="n" s="5">
         <v>45226</v>
@@ -10781,7 +10926,7 @@
         <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G104" t="n" s="5">
         <v>45212</v>
@@ -10810,7 +10955,7 @@
         <v>237</v>
       </c>
       <c r="F105" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G105" t="n" s="5">
         <v>45216</v>
@@ -10839,7 +10984,7 @@
         <v>237</v>
       </c>
       <c r="F106" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G106" t="n" s="5">
         <v>45226</v>
@@ -10868,7 +11013,7 @@
         <v>237</v>
       </c>
       <c r="F107" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G107" t="n" s="5">
         <v>44540</v>
@@ -10897,7 +11042,7 @@
         <v>237</v>
       </c>
       <c r="F108" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G108" t="n" s="5">
         <v>44563</v>
@@ -10926,7 +11071,7 @@
         <v>237</v>
       </c>
       <c r="F109" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G109" t="n" s="5">
         <v>44573</v>
@@ -10955,7 +11100,7 @@
         <v>237</v>
       </c>
       <c r="F110" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G110" t="n" s="5">
         <v>45485</v>
@@ -10984,7 +11129,7 @@
         <v>237</v>
       </c>
       <c r="F111" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G111" t="n" s="5">
         <v>45504</v>
@@ -11013,7 +11158,7 @@
         <v>237</v>
       </c>
       <c r="F112" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G112" t="n" s="5">
         <v>45504</v>
@@ -11042,7 +11187,7 @@
         <v>237</v>
       </c>
       <c r="F113" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G113" t="n" s="5">
         <v>45219</v>
@@ -11071,7 +11216,7 @@
         <v>237</v>
       </c>
       <c r="F114" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G114" t="n" s="5">
         <v>45223</v>
@@ -11100,7 +11245,7 @@
         <v>237</v>
       </c>
       <c r="F115" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G115" t="n" s="5">
         <v>45233</v>
@@ -11129,7 +11274,7 @@
         <v>237</v>
       </c>
       <c r="F116" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G116" t="n" s="5">
         <v>45219</v>
@@ -11158,7 +11303,7 @@
         <v>237</v>
       </c>
       <c r="F117" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G117" t="n" s="5">
         <v>45223</v>
@@ -11187,7 +11332,7 @@
         <v>237</v>
       </c>
       <c r="F118" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G118" t="n" s="5">
         <v>45233</v>
@@ -11216,7 +11361,7 @@
         <v>237</v>
       </c>
       <c r="F119" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G119" t="n" s="5">
         <v>45382</v>
@@ -11245,7 +11390,7 @@
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G120" t="n" s="5">
         <v>45402</v>
@@ -11274,7 +11419,7 @@
         <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G121" t="n" s="5">
         <v>45412</v>
@@ -11303,7 +11448,7 @@
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G122" t="n" s="5">
         <v>45322</v>
@@ -11332,7 +11477,7 @@
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G123" t="n" s="5">
         <v>45331</v>
@@ -11361,7 +11506,7 @@
         <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G124" t="n" s="5">
         <v>45341</v>
@@ -11390,7 +11535,7 @@
         <v>237</v>
       </c>
       <c r="F125" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G125" t="n" s="5">
         <v>45268</v>
@@ -11419,7 +11564,7 @@
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G126" t="n" s="5">
         <v>45313</v>
@@ -11448,7 +11593,7 @@
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G127" t="n" s="5">
         <v>45323</v>
@@ -11477,7 +11622,7 @@
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G128" t="n" s="5">
         <v>45382</v>
@@ -11506,7 +11651,7 @@
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G129" t="n" s="5">
         <v>45402</v>
@@ -11535,7 +11680,7 @@
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G130" t="n" s="5">
         <v>45412</v>
@@ -11564,7 +11709,7 @@
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G131" t="n" s="5">
         <v>45268</v>
@@ -11593,7 +11738,7 @@
         <v>237</v>
       </c>
       <c r="F132" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G132" t="n" s="5">
         <v>45265</v>
@@ -11622,7 +11767,7 @@
         <v>237</v>
       </c>
       <c r="F133" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G133" t="n" s="5">
         <v>45275</v>
@@ -11651,7 +11796,7 @@
         <v>237</v>
       </c>
       <c r="F134" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G134" t="n" s="5">
         <v>45322</v>
@@ -11680,7 +11825,7 @@
         <v>237</v>
       </c>
       <c r="F135" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G135" t="n" s="5">
         <v>45331</v>
@@ -11709,7 +11854,7 @@
         <v>237</v>
       </c>
       <c r="F136" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G136" t="n" s="5">
         <v>45341</v>
@@ -11738,7 +11883,7 @@
         <v>237</v>
       </c>
       <c r="F137" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G137" t="n" s="5">
         <v>45322</v>
@@ -11767,7 +11912,7 @@
         <v>237</v>
       </c>
       <c r="F138" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G138" t="n" s="5">
         <v>45335</v>
@@ -11796,7 +11941,7 @@
         <v>237</v>
       </c>
       <c r="F139" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G139" t="n" s="5">
         <v>45345</v>
@@ -11825,7 +11970,7 @@
         <v>237</v>
       </c>
       <c r="F140" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G140" t="n" s="5">
         <v>45351</v>
@@ -11854,7 +11999,7 @@
         <v>237</v>
       </c>
       <c r="F141" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G141" t="n" s="5">
         <v>45363</v>
@@ -11883,7 +12028,7 @@
         <v>237</v>
       </c>
       <c r="F142" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G142" t="n" s="5">
         <v>45373</v>
@@ -11912,7 +12057,7 @@
         <v>237</v>
       </c>
       <c r="F143" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G143" t="n" s="5">
         <v>45429</v>
@@ -11941,7 +12086,7 @@
         <v>237</v>
       </c>
       <c r="F144" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G144" t="n" s="5">
         <v>45433</v>
@@ -11970,7 +12115,7 @@
         <v>237</v>
       </c>
       <c r="F145" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G145" t="n" s="5">
         <v>45443</v>
@@ -11999,7 +12144,7 @@
         <v>237</v>
       </c>
       <c r="F146" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G146" t="n" s="5">
         <v>45565</v>
@@ -12028,7 +12173,7 @@
         <v>237</v>
       </c>
       <c r="F147" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G147" t="n" s="5">
         <v>45562</v>
@@ -12057,7 +12202,7 @@
         <v>237</v>
       </c>
       <c r="F148" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G148" t="n" s="5">
         <v>45572</v>
@@ -12086,7 +12231,7 @@
         <v>237</v>
       </c>
       <c r="F149" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G149" t="n" s="5">
         <v>45453</v>
@@ -12117,7 +12262,7 @@
         <v>237</v>
       </c>
       <c r="F150" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G150" t="n" s="5">
         <v>45583</v>
@@ -12148,7 +12293,7 @@
         <v>237</v>
       </c>
       <c r="F151" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="G151" t="n" s="5">
         <v>45708</v>
@@ -12179,7 +12324,7 @@
         <v>237</v>
       </c>
       <c r="F152" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G152" t="n" s="5">
         <v>45862</v>
@@ -12210,7 +12355,7 @@
         <v>237</v>
       </c>
       <c r="F153" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G153" t="n" s="5">
         <v>45863</v>
@@ -12241,7 +12386,7 @@
         <v>237</v>
       </c>
       <c r="F154" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G154" t="n" s="5">
         <v>45457</v>
@@ -12270,7 +12415,7 @@
         <v>237</v>
       </c>
       <c r="F155" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G155" t="n" s="5">
         <v>45468</v>
@@ -12299,7 +12444,7 @@
         <v>237</v>
       </c>
       <c r="F156" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G156" t="n" s="5">
         <v>45478</v>
@@ -12328,7 +12473,7 @@
         <v>237</v>
       </c>
       <c r="F157" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G157" t="n" s="5">
         <v>45562</v>
@@ -12359,7 +12504,7 @@
         <v>237</v>
       </c>
       <c r="F158" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G158" t="n" s="5">
         <v>45681</v>
@@ -12390,7 +12535,7 @@
         <v>237</v>
       </c>
       <c r="F159" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G159" t="n" s="5">
         <v>45709</v>
@@ -12421,7 +12566,7 @@
         <v>237</v>
       </c>
       <c r="F160" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G160" t="n" s="5">
         <v>45744</v>
@@ -12452,7 +12597,7 @@
         <v>237</v>
       </c>
       <c r="F161" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G161" t="n" s="5">
         <v>45745</v>
@@ -12483,7 +12628,7 @@
         <v>237</v>
       </c>
       <c r="F162" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G162" t="n" s="5">
         <v>45793</v>
@@ -12514,7 +12659,7 @@
         <v>237</v>
       </c>
       <c r="F163" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G163" t="n" s="5">
         <v>45794</v>
@@ -12545,7 +12690,7 @@
         <v>237</v>
       </c>
       <c r="F164" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G164" t="n" s="5">
         <v>45838</v>
@@ -12576,7 +12721,7 @@
         <v>237</v>
       </c>
       <c r="F165" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="G165" t="n" s="5">
         <v>45562</v>
@@ -12605,7 +12750,7 @@
         <v>237</v>
       </c>
       <c r="F166" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G166" t="n" s="5">
         <v>45586</v>
@@ -12634,7 +12779,7 @@
         <v>237</v>
       </c>
       <c r="F167" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G167" t="n" s="5">
         <v>45596</v>
@@ -12663,7 +12808,7 @@
         <v>237</v>
       </c>
       <c r="F168" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G168" t="n" s="5">
         <v>45534</v>
@@ -12692,7 +12837,7 @@
         <v>237</v>
       </c>
       <c r="F169" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G169" t="n" s="5">
         <v>45552</v>
@@ -12721,7 +12866,7 @@
         <v>237</v>
       </c>
       <c r="F170" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G170" t="n" s="5">
         <v>45562</v>
@@ -12750,7 +12895,7 @@
         <v>237</v>
       </c>
       <c r="F171" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G171" t="n" s="5">
         <v>45754</v>
@@ -12781,7 +12926,7 @@
         <v>237</v>
       </c>
       <c r="F172" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G172" t="n" s="5">
         <v>45772</v>
@@ -12814,7 +12959,7 @@
         <v>237</v>
       </c>
       <c r="F173" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="G173" t="n" s="5">
         <v>45807</v>
@@ -12845,7 +12990,7 @@
         <v>237</v>
       </c>
       <c r="F174" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G174" t="n" s="5">
         <v>45835</v>
@@ -12876,7 +13021,7 @@
         <v>237</v>
       </c>
       <c r="F175" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G175" t="n" s="5">
         <v>45898</v>
@@ -12907,7 +13052,7 @@
         <v>237</v>
       </c>
       <c r="F176" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G176" t="n" s="5">
         <v>43990</v>
@@ -12936,7 +13081,7 @@
         <v>237</v>
       </c>
       <c r="F177" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G177" t="n" s="5">
         <v>44081</v>
@@ -12965,7 +13110,7 @@
         <v>237</v>
       </c>
       <c r="F178" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G178" t="n" s="5">
         <v>44133</v>
@@ -12994,7 +13139,7 @@
         <v>237</v>
       </c>
       <c r="F179" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G179" t="n" s="5">
         <v>44165</v>
@@ -13023,7 +13168,7 @@
         <v>237</v>
       </c>
       <c r="F180" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G180" t="n" s="5">
         <v>44165</v>
@@ -13052,7 +13197,7 @@
         <v>237</v>
       </c>
       <c r="F181" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G181" t="n" s="5">
         <v>44358</v>
@@ -13081,7 +13226,7 @@
         <v>237</v>
       </c>
       <c r="F182" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G182" t="n" s="5">
         <v>44358</v>
@@ -13110,7 +13255,7 @@
         <v>237</v>
       </c>
       <c r="F183" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G183" t="n" s="5">
         <v>44469</v>
@@ -13139,7 +13284,7 @@
         <v>237</v>
       </c>
       <c r="F184" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G184" t="n" s="5">
         <v>45818</v>
@@ -13170,7 +13315,7 @@
         <v>237</v>
       </c>
       <c r="F185" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G185" t="n" s="5">
         <v>45825</v>
@@ -13201,7 +13346,7 @@
         <v>237</v>
       </c>
       <c r="F186" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G186" t="n" s="5">
         <v>45835</v>
@@ -13232,7 +13377,7 @@
         <v>237</v>
       </c>
       <c r="F187" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G187" t="n" s="5">
         <v>45905</v>
@@ -13263,7 +13408,7 @@
         <v>237</v>
       </c>
       <c r="F188" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G188" t="n" s="5">
         <v>45926</v>
@@ -13294,7 +13439,7 @@
         <v>237</v>
       </c>
       <c r="F189" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G189" t="n" s="5">
         <v>45940</v>
@@ -13325,7 +13470,7 @@
         <v>237</v>
       </c>
       <c r="F190" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G190" t="n" s="5">
         <v>45744</v>
@@ -13356,7 +13501,7 @@
         <v>237</v>
       </c>
       <c r="F191" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G191" t="n" s="5">
         <v>45768</v>
@@ -13387,7 +13532,7 @@
         <v>237</v>
       </c>
       <c r="F192" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G192" t="n" s="5">
         <v>45796</v>
@@ -13418,7 +13563,7 @@
         <v>237</v>
       </c>
       <c r="F193" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G193" t="n" s="5">
         <v>45828</v>
@@ -13449,7 +13594,7 @@
         <v>237</v>
       </c>
       <c r="F194" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G194" t="n" s="5">
         <v>45869</v>
@@ -13480,7 +13625,7 @@
         <v>237</v>
       </c>
       <c r="F195" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G195" t="n" s="5">
         <v>45905</v>
@@ -13511,7 +13656,7 @@
         <v>237</v>
       </c>
       <c r="F196" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G196" t="n" s="5">
         <v>45940</v>
@@ -13542,7 +13687,7 @@
         <v>237</v>
       </c>
       <c r="F197" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G197" t="n" s="5">
         <v>45954</v>
@@ -13573,7 +13718,7 @@
         <v>237</v>
       </c>
       <c r="F198" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G198" t="n" s="5">
         <v>45982</v>
@@ -13604,7 +13749,7 @@
         <v>237</v>
       </c>
       <c r="F199" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G199" t="n" s="5">
         <v>45989</v>
@@ -13633,7 +13778,7 @@
         <v>237</v>
       </c>
       <c r="F200" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G200" t="n" s="5">
         <v>46010</v>
@@ -13662,7 +13807,7 @@
         <v>237</v>
       </c>
       <c r="F201" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G201" t="n" s="5">
         <v>45798</v>
@@ -13693,7 +13838,7 @@
         <v>237</v>
       </c>
       <c r="F202" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G202" t="n" s="5">
         <v>45806</v>
@@ -13724,7 +13869,7 @@
         <v>237</v>
       </c>
       <c r="F203" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G203" t="n" s="5">
         <v>45814</v>
@@ -13755,7 +13900,7 @@
         <v>237</v>
       </c>
       <c r="F204" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G204" t="n" s="5">
         <v>45863</v>
@@ -13786,7 +13931,7 @@
         <v>237</v>
       </c>
       <c r="F205" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G205" t="n" s="5">
         <v>45877</v>
@@ -13817,7 +13962,7 @@
         <v>237</v>
       </c>
       <c r="F206" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G206" t="n" s="5">
         <v>45884</v>
@@ -13848,7 +13993,7 @@
         <v>237</v>
       </c>
       <c r="F207" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G207" t="n" s="5">
         <v>45863</v>
@@ -13879,7 +14024,7 @@
         <v>237</v>
       </c>
       <c r="F208" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G208" t="n" s="5">
         <v>45877</v>
@@ -13910,7 +14055,7 @@
         <v>237</v>
       </c>
       <c r="F209" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G209" t="n" s="5">
         <v>45884</v>
@@ -13941,7 +14086,7 @@
         <v>237</v>
       </c>
       <c r="F210" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G210" t="n" s="5">
         <v>45863</v>
@@ -13972,7 +14117,7 @@
         <v>237</v>
       </c>
       <c r="F211" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G211" t="n" s="5">
         <v>45877</v>
@@ -14003,7 +14148,7 @@
         <v>237</v>
       </c>
       <c r="F212" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G212" t="n" s="5">
         <v>45884</v>
@@ -14034,7 +14179,7 @@
         <v>237</v>
       </c>
       <c r="F213" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G213" t="n" s="5">
         <v>45961</v>
@@ -14065,7 +14210,7 @@
         <v>237</v>
       </c>
       <c r="F214" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G214" t="n" s="5">
         <v>46010</v>
@@ -14096,7 +14241,7 @@
         <v>237</v>
       </c>
       <c r="F215" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G215" t="n" s="5">
         <v>46045</v>
@@ -14127,7 +14272,7 @@
         <v>237</v>
       </c>
       <c r="F216" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G216" t="n" s="5">
         <v>45929</v>
@@ -14158,7 +14303,7 @@
         <v>237</v>
       </c>
       <c r="F217" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G217" t="n" s="5">
         <v>45936</v>
@@ -14189,7 +14334,7 @@
         <v>237</v>
       </c>
       <c r="F218" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G218" t="n" s="5">
         <v>45954</v>
@@ -14220,7 +14365,7 @@
         <v>237</v>
       </c>
       <c r="F219" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G219" t="n" s="5">
         <v>45922</v>
@@ -14251,7 +14396,7 @@
         <v>237</v>
       </c>
       <c r="F220" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G220" t="n" s="5">
         <v>45926</v>
@@ -14282,7 +14427,7 @@
         <v>237</v>
       </c>
       <c r="F221" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G221" t="n" s="5">
         <v>45940</v>
@@ -14313,7 +14458,7 @@
         <v>237</v>
       </c>
       <c r="F222" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G222" t="n" s="5">
         <v>45953</v>
@@ -14344,7 +14489,7 @@
         <v>237</v>
       </c>
       <c r="F223" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G223" t="n" s="5">
         <v>45961</v>
@@ -14375,7 +14520,7 @@
         <v>237</v>
       </c>
       <c r="F224" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G224" t="n" s="5">
         <v>45975</v>
@@ -14406,7 +14551,7 @@
         <v>237</v>
       </c>
       <c r="F225" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G225" t="n" s="5">
         <v>46052</v>
@@ -14437,7 +14582,7 @@
         <v>237</v>
       </c>
       <c r="F226" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G226" t="n" s="5">
         <v>46066</v>
@@ -14468,7 +14613,7 @@
         <v>237</v>
       </c>
       <c r="F227" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G227" t="n" s="5">
         <v>46080</v>
@@ -14499,7 +14644,7 @@
         <v>237</v>
       </c>
       <c r="F228" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G228" t="n" s="5">
         <v>45947</v>
@@ -14530,7 +14675,7 @@
         <v>237</v>
       </c>
       <c r="F229" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G229" t="n" s="5">
         <v>45954</v>
@@ -14561,7 +14706,7 @@
         <v>237</v>
       </c>
       <c r="F230" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G230" t="n" s="5">
         <v>45968</v>
@@ -14592,7 +14737,7 @@
         <v>237</v>
       </c>
       <c r="F231" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G231" t="n" s="5">
         <v>45926</v>
@@ -14623,7 +14768,7 @@
         <v>237</v>
       </c>
       <c r="F232" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G232" t="n" s="5">
         <v>45933</v>
@@ -14654,7 +14799,7 @@
         <v>237</v>
       </c>
       <c r="F233" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G233" t="n" s="5">
         <v>45947</v>
@@ -14685,7 +14830,7 @@
         <v>237</v>
       </c>
       <c r="F234" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G234" t="n" s="5">
         <v>45960</v>
@@ -14716,7 +14861,7 @@
         <v>237</v>
       </c>
       <c r="F235" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G235" t="n" s="5">
         <v>45967</v>
@@ -14747,7 +14892,7 @@
         <v>237</v>
       </c>
       <c r="F236" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G236" t="n" s="5">
         <v>45982</v>
@@ -14778,7 +14923,7 @@
         <v>237</v>
       </c>
       <c r="F237" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="G237" t="n" s="5">
         <v>46010</v>
@@ -14809,7 +14954,7 @@
         <v>237</v>
       </c>
       <c r="F238" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G238" t="n" s="5">
         <v>46052</v>
@@ -14840,7 +14985,7 @@
         <v>237</v>
       </c>
       <c r="F239" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G239" t="n" s="5">
         <v>46003</v>
@@ -14871,7 +15016,7 @@
         <v>237</v>
       </c>
       <c r="F240" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G240" t="n" s="5">
         <v>46010</v>
@@ -14902,7 +15047,7 @@
         <v>237</v>
       </c>
       <c r="F241" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G241" t="n" s="5">
         <v>46031</v>
@@ -14933,7 +15078,7 @@
         <v>237</v>
       </c>
       <c r="F242" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G242" t="n" s="5">
         <v>46269</v>
@@ -14964,7 +15109,7 @@
         <v>237</v>
       </c>
       <c r="F243" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G243" t="n" s="5">
         <v>46276</v>
@@ -14995,7 +15140,7 @@
         <v>237</v>
       </c>
       <c r="F244" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G244" t="n" s="5">
         <v>46290</v>
@@ -15006,6 +15151,168 @@
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="5"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>511</v>
+      </c>
+      <c r="B245" t="s">
+        <v>512</v>
+      </c>
+      <c r="C245" t="s">
+        <v>246</v>
+      </c>
+      <c r="D245" t="s">
+        <v>477</v>
+      </c>
+      <c r="E245" t="s">
+        <v>237</v>
+      </c>
+      <c r="F245" t="s">
+        <v>531</v>
+      </c>
+      <c r="G245" t="n" s="5">
+        <v>46325</v>
+      </c>
+      <c r="H245" s="5"/>
+      <c r="I245" s="5"/>
+      <c r="J245" s="5"/>
+      <c r="K245" s="5"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>511</v>
+      </c>
+      <c r="B246" t="s">
+        <v>512</v>
+      </c>
+      <c r="C246" t="s">
+        <v>246</v>
+      </c>
+      <c r="D246" t="s">
+        <v>477</v>
+      </c>
+      <c r="E246" t="s">
+        <v>237</v>
+      </c>
+      <c r="F246" t="s">
+        <v>530</v>
+      </c>
+      <c r="G246" t="n" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H246" s="5"/>
+      <c r="I246" s="5"/>
+      <c r="J246" s="5"/>
+      <c r="K246" s="5"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>511</v>
+      </c>
+      <c r="B247" t="s">
+        <v>512</v>
+      </c>
+      <c r="C247" t="s">
+        <v>246</v>
+      </c>
+      <c r="D247" t="s">
+        <v>477</v>
+      </c>
+      <c r="E247" t="s">
+        <v>237</v>
+      </c>
+      <c r="F247" t="s">
+        <v>522</v>
+      </c>
+      <c r="G247" t="n" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H247" s="5"/>
+      <c r="I247" s="5"/>
+      <c r="J247" s="5"/>
+      <c r="K247" s="5"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>515</v>
+      </c>
+      <c r="B248" t="s">
+        <v>516</v>
+      </c>
+      <c r="C248" t="s">
+        <v>246</v>
+      </c>
+      <c r="D248" t="s">
+        <v>247</v>
+      </c>
+      <c r="E248" t="s">
+        <v>237</v>
+      </c>
+      <c r="F248" t="s">
+        <v>523</v>
+      </c>
+      <c r="G248" t="n" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H248" s="5"/>
+      <c r="I248" s="5"/>
+      <c r="J248" s="5"/>
+      <c r="K248" s="5"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>515</v>
+      </c>
+      <c r="B249" t="s">
+        <v>516</v>
+      </c>
+      <c r="C249" t="s">
+        <v>246</v>
+      </c>
+      <c r="D249" t="s">
+        <v>247</v>
+      </c>
+      <c r="E249" t="s">
+        <v>237</v>
+      </c>
+      <c r="F249" t="s">
+        <v>521</v>
+      </c>
+      <c r="G249" t="n" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H249" s="5"/>
+      <c r="I249" s="5"/>
+      <c r="J249" s="5"/>
+      <c r="K249" s="5"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>515</v>
+      </c>
+      <c r="B250" t="s">
+        <v>516</v>
+      </c>
+      <c r="C250" t="s">
+        <v>246</v>
+      </c>
+      <c r="D250" t="s">
+        <v>247</v>
+      </c>
+      <c r="E250" t="s">
+        <v>237</v>
+      </c>
+      <c r="F250" t="s">
+        <v>522</v>
+      </c>
+      <c r="G250" t="n" s="5">
+        <v>46360</v>
+      </c>
+      <c r="H250" s="5"/>
+      <c r="I250" s="5"/>
+      <c r="J250" s="5"/>
+      <c r="K250" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15070,23 +15377,23 @@
         <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F2" t="n" s="3">
         <v>89586</v>
       </c>
       <c r="G2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H2"/>
       <c r="I2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -15100,29 +15407,29 @@
         <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D3" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F3" t="n" s="3">
         <v>894900</v>
       </c>
       <c r="G3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K3" t="s">
         <v>535</v>
-      </c>
-      <c r="K3" t="s">
-        <v>528</v>
       </c>
       <c r="L3"/>
     </row>
@@ -15134,29 +15441,29 @@
         <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D4" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E4" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F4" t="n" s="3">
         <v>894900</v>
       </c>
       <c r="G4" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J4" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="K4" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L4"/>
     </row>
@@ -15168,29 +15475,29 @@
         <v>343</v>
       </c>
       <c r="C5" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D5" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E5" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F5" t="n" s="3">
         <v>1187000</v>
       </c>
       <c r="G5" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J5" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K5" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L5"/>
     </row>
@@ -15202,29 +15509,29 @@
         <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D6" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E6" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F6" t="n" s="3">
         <v>1187000</v>
       </c>
       <c r="G6" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J6" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="K6" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L6"/>
     </row>
@@ -15236,23 +15543,23 @@
         <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D7" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="E7" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F7" t="n" s="3">
         <v>1092000</v>
       </c>
       <c r="G7" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
@@ -15266,29 +15573,29 @@
         <v>343</v>
       </c>
       <c r="C8" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D8" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E8" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F8" t="n" s="3">
         <v>1040253.08</v>
       </c>
       <c r="G8" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J8" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="K8" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L8"/>
     </row>
@@ -15300,29 +15607,29 @@
         <v>343</v>
       </c>
       <c r="C9" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D9" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E9" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F9" t="n" s="3">
         <v>1040253.08</v>
       </c>
       <c r="G9" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J9" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K9" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="L9"/>
     </row>
@@ -15334,23 +15641,23 @@
         <v>343</v>
       </c>
       <c r="C10" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D10" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E10" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F10" t="n" s="3">
         <v>1199094.05</v>
       </c>
       <c r="G10" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -15364,23 +15671,23 @@
         <v>343</v>
       </c>
       <c r="C11" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D11" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E11" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F11" t="n" s="3">
         <v>1072823.25</v>
       </c>
       <c r="G11" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J11"/>
       <c r="K11"/>
@@ -15394,23 +15701,23 @@
         <v>427</v>
       </c>
       <c r="C12" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="D12" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E12" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F12" t="n" s="3">
         <v>8890403.41</v>
       </c>
       <c r="G12" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -15424,23 +15731,23 @@
         <v>427</v>
       </c>
       <c r="C13" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D13" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="E13" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F13" t="n" s="3">
         <v>10762326.94</v>
       </c>
       <c r="G13" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H13"/>
       <c r="I13" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J13"/>
       <c r="K13"/>
@@ -15454,23 +15761,23 @@
         <v>427</v>
       </c>
       <c r="C14" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D14" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="E14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F14" t="n" s="3">
         <v>11052447.36</v>
       </c>
       <c r="G14" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H14"/>
       <c r="I14" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J14"/>
       <c r="K14"/>
@@ -15484,29 +15791,29 @@
         <v>437</v>
       </c>
       <c r="C15" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="D15" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E15" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F15" t="n" s="3">
         <v>2673364.65</v>
       </c>
       <c r="G15" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H15"/>
       <c r="I15" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J15" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="K15" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L15"/>
     </row>
@@ -15518,29 +15825,29 @@
         <v>437</v>
       </c>
       <c r="C16" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="D16" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E16" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F16" t="n" s="3">
         <v>2673364.65</v>
       </c>
       <c r="G16" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H16"/>
       <c r="I16" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J16" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="K16" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L16"/>
     </row>
@@ -15552,29 +15859,29 @@
         <v>437</v>
       </c>
       <c r="C17" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D17" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E17" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F17" t="n" s="3">
         <v>2906774.76</v>
       </c>
       <c r="G17" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H17"/>
       <c r="I17" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J17" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="K17" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L17"/>
     </row>
@@ -15586,29 +15893,29 @@
         <v>437</v>
       </c>
       <c r="C18" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D18" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E18" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F18" t="n" s="3">
         <v>2906774.76</v>
       </c>
       <c r="G18" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H18"/>
       <c r="I18" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J18" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="K18" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="L18"/>
     </row>
@@ -15620,29 +15927,29 @@
         <v>437</v>
       </c>
       <c r="C19" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D19" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E19" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F19" t="n" s="3">
         <v>2839624.81</v>
       </c>
       <c r="G19" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H19"/>
       <c r="I19" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J19" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="K19" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L19"/>
     </row>
@@ -15654,29 +15961,29 @@
         <v>437</v>
       </c>
       <c r="C20" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D20" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E20" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F20" t="n" s="3">
         <v>2839624.81</v>
       </c>
       <c r="G20" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J20" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="K20" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L20"/>
     </row>
@@ -15688,29 +15995,29 @@
         <v>437</v>
       </c>
       <c r="C21" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D21" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E21" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F21" t="n" s="3">
         <v>2839624.81</v>
       </c>
       <c r="G21" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H21"/>
       <c r="I21" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J21" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="K21" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L21"/>
     </row>
@@ -15722,23 +16029,23 @@
         <v>437</v>
       </c>
       <c r="C22" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="D22" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="E22" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F22" t="n" s="3">
         <v>3213435</v>
       </c>
       <c r="G22" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
@@ -15752,29 +16059,29 @@
         <v>437</v>
       </c>
       <c r="C23" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="D23" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E23" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F23" t="n" s="3">
         <v>2715200</v>
       </c>
       <c r="G23" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H23"/>
       <c r="I23" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J23" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="K23" t="s">
-        <v>528</v>
+        <v>578</v>
       </c>
       <c r="L23"/>
     </row>
@@ -15786,29 +16093,29 @@
         <v>437</v>
       </c>
       <c r="C24" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="D24" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E24" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F24" t="n" s="3">
         <v>2715200</v>
       </c>
       <c r="G24" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J24" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K24" t="s">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="L24"/>
     </row>
@@ -15820,29 +16127,29 @@
         <v>437</v>
       </c>
       <c r="C25" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="D25" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E25" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F25" t="n" s="3">
         <v>2546548.16</v>
       </c>
       <c r="G25" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H25"/>
       <c r="I25" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J25" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="K25" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L25"/>
     </row>
@@ -15854,29 +16161,29 @@
         <v>437</v>
       </c>
       <c r="C26" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="D26" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E26" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F26" t="n" s="3">
         <v>2546548.16</v>
       </c>
       <c r="G26" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J26" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="K26" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="L26"/>
     </row>
@@ -15888,29 +16195,29 @@
         <v>451</v>
       </c>
       <c r="C27" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="D27" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E27" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F27" t="n" s="3">
         <v>24176706.05</v>
       </c>
       <c r="G27" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J27" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="K27" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L27"/>
     </row>
@@ -15922,29 +16229,29 @@
         <v>451</v>
       </c>
       <c r="C28" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="D28" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E28" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F28" t="n" s="3">
         <v>24176706.05</v>
       </c>
       <c r="G28" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J28" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K28" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L28"/>
     </row>
@@ -15956,23 +16263,23 @@
         <v>451</v>
       </c>
       <c r="C29" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E29" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F29" t="n" s="3">
         <v>20122500</v>
       </c>
       <c r="G29" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H29"/>
       <c r="I29" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J29"/>
       <c r="K29"/>
@@ -15986,23 +16293,23 @@
         <v>451</v>
       </c>
       <c r="C30" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D30" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E30" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F30" t="n" s="3">
         <v>16269331.92</v>
       </c>
       <c r="G30" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H30"/>
       <c r="I30" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J30"/>
       <c r="K30"/>
@@ -16016,23 +16323,23 @@
         <v>451</v>
       </c>
       <c r="C31" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D31" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="E31" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F31" t="n" s="3">
         <v>22753496.13</v>
       </c>
       <c r="G31" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J31"/>
       <c r="K31"/>
@@ -16046,23 +16353,23 @@
         <v>451</v>
       </c>
       <c r="C32" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="D32" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E32" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F32" t="n" s="3">
         <v>16228968.43</v>
       </c>
       <c r="G32" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J32"/>
       <c r="K32"/>
@@ -16076,19 +16383,19 @@
         <v>460</v>
       </c>
       <c r="C33" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="D33" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="3"/>
       <c r="G33" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H33"/>
       <c r="I33" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J33"/>
       <c r="K33"/>
@@ -16102,19 +16409,19 @@
         <v>460</v>
       </c>
       <c r="C34" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="3"/>
       <c r="G34" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H34"/>
       <c r="I34" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J34"/>
       <c r="K34"/>
@@ -16128,19 +16435,19 @@
         <v>460</v>
       </c>
       <c r="C35" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="D35" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="3"/>
       <c r="G35" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H35"/>
       <c r="I35" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J35"/>
       <c r="K35"/>
@@ -16154,19 +16461,19 @@
         <v>464</v>
       </c>
       <c r="C36" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="D36" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="3"/>
       <c r="G36" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H36"/>
       <c r="I36" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J36"/>
       <c r="K36"/>
@@ -16180,19 +16487,19 @@
         <v>464</v>
       </c>
       <c r="C37" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="D37" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="3"/>
       <c r="G37" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H37"/>
       <c r="I37" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J37"/>
       <c r="K37"/>
@@ -16206,19 +16513,19 @@
         <v>464</v>
       </c>
       <c r="C38" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D38" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E38"/>
       <c r="F38" s="3"/>
       <c r="G38" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H38"/>
       <c r="I38" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
@@ -16232,19 +16539,19 @@
         <v>466</v>
       </c>
       <c r="C39" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="D39" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E39"/>
       <c r="F39" s="3"/>
       <c r="G39" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H39"/>
       <c r="I39" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J39"/>
       <c r="K39"/>
@@ -16258,19 +16565,19 @@
         <v>466</v>
       </c>
       <c r="C40" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="D40" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E40"/>
       <c r="F40" s="3"/>
       <c r="G40" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H40"/>
       <c r="I40" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J40"/>
       <c r="K40"/>
@@ -16284,19 +16591,19 @@
         <v>466</v>
       </c>
       <c r="C41" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D41" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E41"/>
       <c r="F41" s="3"/>
       <c r="G41" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H41"/>
       <c r="I41" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J41"/>
       <c r="K41"/>
@@ -16310,23 +16617,23 @@
         <v>468</v>
       </c>
       <c r="C42" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="D42" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="E42" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F42" t="n" s="3">
         <v>2766626.51</v>
       </c>
       <c r="G42" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J42"/>
       <c r="K42"/>
@@ -16340,29 +16647,29 @@
         <v>468</v>
       </c>
       <c r="C43" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="D43" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E43" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F43" t="n" s="3">
         <v>2311586</v>
       </c>
       <c r="G43" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J43" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="K43" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L43"/>
     </row>
@@ -16374,29 +16681,29 @@
         <v>468</v>
       </c>
       <c r="C44" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="D44" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E44" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F44" t="n" s="3">
         <v>2311586</v>
       </c>
       <c r="G44" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J44" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="K44" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L44"/>
     </row>
@@ -16408,23 +16715,23 @@
         <v>468</v>
       </c>
       <c r="C45" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="D45" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E45" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F45" t="n" s="3">
         <v>2265050.3</v>
       </c>
       <c r="G45" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J45"/>
       <c r="K45"/>
@@ -16438,23 +16745,23 @@
         <v>468</v>
       </c>
       <c r="C46" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="D46" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E46" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F46" t="n" s="3">
         <v>2082559.73</v>
       </c>
       <c r="G46" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H46"/>
       <c r="I46" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J46"/>
       <c r="K46"/>
@@ -16468,29 +16775,29 @@
         <v>468</v>
       </c>
       <c r="C47" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D47" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E47" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F47" t="n" s="3">
         <v>3170790.96</v>
       </c>
       <c r="G47" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H47"/>
       <c r="I47" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J47" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="K47" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L47"/>
     </row>
@@ -16502,29 +16809,29 @@
         <v>468</v>
       </c>
       <c r="C48" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D48" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E48" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F48" t="n" s="3">
         <v>3170790.96</v>
       </c>
       <c r="G48" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J48" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="K48" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L48"/>
     </row>
@@ -16536,29 +16843,29 @@
         <v>468</v>
       </c>
       <c r="C49" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="D49" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E49" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F49" t="n" s="3">
         <v>3530575</v>
       </c>
       <c r="G49" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J49" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="K49" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="L49"/>
     </row>
@@ -16570,29 +16877,29 @@
         <v>468</v>
       </c>
       <c r="C50" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="D50" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E50" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F50" t="n" s="3">
         <v>3530575</v>
       </c>
       <c r="G50" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H50"/>
       <c r="I50" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J50" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="K50" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L50"/>
     </row>
@@ -16604,19 +16911,19 @@
         <v>474</v>
       </c>
       <c r="C51" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="D51" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E51"/>
       <c r="F51" s="3"/>
       <c r="G51" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H51"/>
       <c r="I51" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J51"/>
       <c r="K51"/>
@@ -16630,19 +16937,19 @@
         <v>474</v>
       </c>
       <c r="C52" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D52" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E52"/>
       <c r="F52" s="3"/>
       <c r="G52" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H52"/>
       <c r="I52" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J52"/>
       <c r="K52"/>
@@ -16656,19 +16963,19 @@
         <v>474</v>
       </c>
       <c r="C53" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D53" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E53"/>
       <c r="F53" s="3"/>
       <c r="G53" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H53"/>
       <c r="I53" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J53"/>
       <c r="K53"/>
@@ -16682,23 +16989,23 @@
         <v>476</v>
       </c>
       <c r="C54" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="D54" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E54" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F54" t="n" s="3">
         <v>15400</v>
       </c>
       <c r="G54" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H54"/>
       <c r="I54" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J54"/>
       <c r="K54"/>
@@ -16712,23 +17019,23 @@
         <v>479</v>
       </c>
       <c r="C55" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="D55" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E55" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F55" t="n" s="3">
         <v>15400</v>
       </c>
       <c r="G55" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H55"/>
       <c r="I55" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J55"/>
       <c r="K55"/>
@@ -16742,23 +17049,23 @@
         <v>481</v>
       </c>
       <c r="C56" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E56" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F56" t="n" s="3">
         <v>15400</v>
       </c>
       <c r="G56" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H56"/>
       <c r="I56" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J56"/>
       <c r="K56"/>
@@ -16772,23 +17079,23 @@
         <v>483</v>
       </c>
       <c r="C57" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D57" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E57" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F57" t="n" s="3">
         <v>59928</v>
       </c>
       <c r="G57" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H57"/>
       <c r="I57" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J57"/>
       <c r="K57"/>
@@ -16802,19 +17109,19 @@
         <v>486</v>
       </c>
       <c r="C58" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="D58" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E58"/>
       <c r="F58" s="3"/>
       <c r="G58" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H58"/>
       <c r="I58" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J58"/>
       <c r="K58"/>
@@ -16828,19 +17135,19 @@
         <v>486</v>
       </c>
       <c r="C59" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="D59" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E59"/>
       <c r="F59" s="3"/>
       <c r="G59" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H59"/>
       <c r="I59" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J59"/>
       <c r="K59"/>
@@ -16854,19 +17161,19 @@
         <v>486</v>
       </c>
       <c r="C60" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="D60" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E60"/>
       <c r="F60" s="3"/>
       <c r="G60" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H60"/>
       <c r="I60" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J60"/>
       <c r="K60"/>
@@ -16880,23 +17187,23 @@
         <v>489</v>
       </c>
       <c r="C61" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="D61" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E61" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F61" t="n" s="3">
         <v>78000</v>
       </c>
       <c r="G61" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H61"/>
       <c r="I61" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J61"/>
       <c r="K61"/>
@@ -16910,23 +17217,23 @@
         <v>355</v>
       </c>
       <c r="C62" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="D62" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E62" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F62" t="n" s="3">
         <v>69600</v>
       </c>
       <c r="G62" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H62"/>
       <c r="I62" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J62"/>
       <c r="K62"/>
@@ -16940,19 +17247,19 @@
         <v>493</v>
       </c>
       <c r="C63" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="D63" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E63"/>
       <c r="F63" s="3"/>
       <c r="G63" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H63"/>
       <c r="I63" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J63"/>
       <c r="K63"/>
@@ -16966,19 +17273,19 @@
         <v>493</v>
       </c>
       <c r="C64" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D64" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E64"/>
       <c r="F64" s="3"/>
       <c r="G64" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H64"/>
       <c r="I64" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J64"/>
       <c r="K64"/>
@@ -16992,19 +17299,19 @@
         <v>493</v>
       </c>
       <c r="C65" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D65" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E65"/>
       <c r="F65" s="3"/>
       <c r="G65" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H65"/>
       <c r="I65" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J65"/>
       <c r="K65"/>
@@ -17018,19 +17325,19 @@
         <v>493</v>
       </c>
       <c r="C66" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="D66" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E66"/>
       <c r="F66" s="3"/>
       <c r="G66" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H66"/>
       <c r="I66" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J66"/>
       <c r="K66"/>
@@ -17044,19 +17351,19 @@
         <v>496</v>
       </c>
       <c r="C67" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="D67" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E67"/>
       <c r="F67" s="3"/>
       <c r="G67" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H67"/>
       <c r="I67" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J67"/>
       <c r="K67"/>
@@ -17070,23 +17377,23 @@
         <v>460</v>
       </c>
       <c r="C68" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="D68" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E68" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F68" t="n" s="3">
         <v>42000</v>
       </c>
       <c r="G68" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H68"/>
       <c r="I68" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J68"/>
       <c r="K68"/>
@@ -17094,29 +17401,29 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B69" t="s">
         <v>476</v>
       </c>
       <c r="C69" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="D69" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E69" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F69" t="n" s="3">
         <v>42000</v>
       </c>
       <c r="G69" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H69"/>
       <c r="I69" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J69"/>
       <c r="K69"/>
@@ -17130,23 +17437,23 @@
         <v>500</v>
       </c>
       <c r="C70" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D70" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E70" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F70" t="n" s="3">
         <v>59928</v>
       </c>
       <c r="G70" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H70"/>
       <c r="I70" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J70"/>
       <c r="K70"/>
@@ -17160,23 +17467,23 @@
         <v>503</v>
       </c>
       <c r="C71" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="D71" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E71" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F71" t="n" s="3">
         <v>189000</v>
       </c>
       <c r="G71" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H71"/>
       <c r="I71" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J71"/>
       <c r="K71"/>
@@ -17190,23 +17497,23 @@
         <v>503</v>
       </c>
       <c r="C72" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="D72" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E72" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F72" t="n" s="3">
         <v>218500</v>
       </c>
       <c r="G72" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H72"/>
       <c r="I72" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J72"/>
       <c r="K72"/>
@@ -17220,23 +17527,23 @@
         <v>503</v>
       </c>
       <c r="C73" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="D73" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E73" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F73" t="n" s="3">
         <v>209000</v>
       </c>
       <c r="G73" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H73"/>
       <c r="I73" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J73"/>
       <c r="K73"/>
@@ -17250,19 +17557,19 @@
         <v>506</v>
       </c>
       <c r="C74" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="D74" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E74"/>
       <c r="F74" s="3"/>
       <c r="G74" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H74"/>
       <c r="I74" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
@@ -17276,19 +17583,19 @@
         <v>506</v>
       </c>
       <c r="C75" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="D75" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E75"/>
       <c r="F75" s="3"/>
       <c r="G75" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H75"/>
       <c r="I75" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J75"/>
       <c r="K75"/>
@@ -17302,23 +17609,23 @@
         <v>508</v>
       </c>
       <c r="C76" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D76" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E76" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F76" t="n" s="3">
         <v>30000</v>
       </c>
       <c r="G76" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="H76"/>
       <c r="I76" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J76"/>
       <c r="K76"/>
@@ -17422,22 +17729,22 @@
         <v>276</v>
       </c>
       <c r="B2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="D2" t="s">
         <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G2" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="H2" t="n" s="5">
         <v>44634</v>
@@ -17452,13 +17759,13 @@
         <v>89586</v>
       </c>
       <c r="L2" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M2" t="n">
         <v>11109</v>
       </c>
       <c r="N2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O2"/>
       <c r="P2"/>
@@ -17469,7 +17776,7 @@
       <c r="U2"/>
       <c r="V2"/>
       <c r="W2" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="X2"/>
     </row>
@@ -17478,22 +17785,22 @@
         <v>342</v>
       </c>
       <c r="B3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C3" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D3" t="s">
         <v>344</v>
       </c>
       <c r="E3" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F3" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G3" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="H3" t="n" s="5">
         <v>45700</v>
@@ -17508,13 +17815,13 @@
         <v>894900</v>
       </c>
       <c r="L3" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="M3" t="n">
         <v>11109</v>
       </c>
       <c r="N3" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O3"/>
       <c r="P3"/>
@@ -17525,7 +17832,7 @@
       <c r="U3"/>
       <c r="V3"/>
       <c r="W3" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="X3"/>
     </row>
@@ -17534,22 +17841,22 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C4" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="D4" t="s">
         <v>428</v>
       </c>
       <c r="E4" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="F4" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G4" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H4" t="n" s="5">
         <v>45792</v>
@@ -17564,13 +17871,13 @@
         <v>8890403.41</v>
       </c>
       <c r="L4" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="M4" t="n">
         <v>11109</v>
       </c>
       <c r="N4" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -17581,7 +17888,7 @@
       <c r="U4"/>
       <c r="V4"/>
       <c r="W4" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="X4"/>
     </row>
@@ -17590,22 +17897,22 @@
         <v>426</v>
       </c>
       <c r="B5" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C5" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="D5" t="s">
         <v>428</v>
       </c>
       <c r="E5" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="F5" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="G5" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H5" t="n" s="5">
         <v>45846</v>
@@ -17620,13 +17927,13 @@
         <v>10762356.94</v>
       </c>
       <c r="L5" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="M5" t="n">
         <v>11109</v>
       </c>
       <c r="N5" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O5"/>
       <c r="P5"/>
@@ -17637,7 +17944,7 @@
       <c r="U5"/>
       <c r="V5"/>
       <c r="W5" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="X5"/>
     </row>
@@ -17646,22 +17953,22 @@
         <v>436</v>
       </c>
       <c r="B6" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C6" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D6" t="s">
         <v>437</v>
       </c>
       <c r="E6" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="F6" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G6" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="H6" t="n" s="5">
         <v>45901</v>
@@ -17676,13 +17983,13 @@
         <v>2715200</v>
       </c>
       <c r="L6" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="M6" t="n">
         <v>11109</v>
       </c>
       <c r="N6" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O6"/>
       <c r="P6"/>
@@ -17693,7 +18000,7 @@
       <c r="U6"/>
       <c r="V6"/>
       <c r="W6" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="X6"/>
     </row>
@@ -17702,22 +18009,22 @@
         <v>450</v>
       </c>
       <c r="B7" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="C7" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="D7" t="s">
         <v>452</v>
       </c>
       <c r="E7" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F7" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G7" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H7" t="n" s="5">
         <v>46010</v>
@@ -17732,13 +18039,13 @@
         <v>16228968.43</v>
       </c>
       <c r="L7" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="M7" t="n">
         <v>20101</v>
       </c>
       <c r="N7" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O7"/>
       <c r="P7"/>
@@ -17749,7 +18056,7 @@
       <c r="U7"/>
       <c r="V7"/>
       <c r="W7" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="X7"/>
     </row>
@@ -17758,22 +18065,22 @@
         <v>459</v>
       </c>
       <c r="B8" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="C8" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="D8" t="s">
         <v>461</v>
       </c>
       <c r="E8" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F8" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G8" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H8" t="n" s="5">
         <v>45849</v>
@@ -17788,13 +18095,13 @@
         <v>23100</v>
       </c>
       <c r="L8" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="M8" t="n">
         <v>11109</v>
       </c>
       <c r="N8" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O8"/>
       <c r="P8"/>
@@ -17805,7 +18112,7 @@
       <c r="U8"/>
       <c r="V8"/>
       <c r="W8" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="X8"/>
     </row>
@@ -17814,22 +18121,22 @@
         <v>463</v>
       </c>
       <c r="B9" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="C9" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="D9" t="s">
         <v>461</v>
       </c>
       <c r="E9" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F9" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G9" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H9" t="n" s="5">
         <v>45968</v>
@@ -17844,13 +18151,13 @@
         <v>52800</v>
       </c>
       <c r="L9" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="M9" t="n">
         <v>11109</v>
       </c>
       <c r="N9" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O9"/>
       <c r="P9"/>
@@ -17861,7 +18168,7 @@
       <c r="U9"/>
       <c r="V9"/>
       <c r="W9" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X9"/>
     </row>
@@ -17870,22 +18177,22 @@
         <v>465</v>
       </c>
       <c r="B10" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C10" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="D10" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="E10" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="F10" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G10" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H10" t="n" s="5">
         <v>45797</v>
@@ -17900,13 +18207,13 @@
         <v>32500</v>
       </c>
       <c r="L10" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="M10" t="n">
         <v>11109</v>
       </c>
       <c r="N10" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O10"/>
       <c r="P10"/>
@@ -17917,7 +18224,7 @@
       <c r="U10"/>
       <c r="V10"/>
       <c r="W10" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X10"/>
     </row>
@@ -17926,22 +18233,22 @@
         <v>473</v>
       </c>
       <c r="B11" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C11" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="D11" t="s">
         <v>461</v>
       </c>
       <c r="E11" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="F11" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G11" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="H11" t="n" s="5">
         <v>45811</v>
@@ -17956,13 +18263,13 @@
         <v>20000</v>
       </c>
       <c r="L11" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="M11" t="n">
         <v>10109</v>
       </c>
       <c r="N11" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O11"/>
       <c r="P11"/>
@@ -17973,7 +18280,7 @@
       <c r="U11"/>
       <c r="V11"/>
       <c r="W11" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X11"/>
     </row>
@@ -17982,22 +18289,22 @@
         <v>475</v>
       </c>
       <c r="B12" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C12" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D12" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="E12" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="F12" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G12" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H12" t="n" s="5">
         <v>45861</v>
@@ -18012,13 +18319,13 @@
         <v>15400</v>
       </c>
       <c r="L12" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="M12" t="n">
         <v>11109</v>
       </c>
       <c r="N12" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O12"/>
       <c r="P12"/>
@@ -18029,7 +18336,7 @@
       <c r="U12"/>
       <c r="V12"/>
       <c r="W12" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X12"/>
     </row>
@@ -18038,22 +18345,22 @@
         <v>478</v>
       </c>
       <c r="B13" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C13" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="D13" t="s">
         <v>461</v>
       </c>
       <c r="E13" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F13" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G13" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H13" t="n" s="5">
         <v>45859</v>
@@ -18068,13 +18375,13 @@
         <v>15400</v>
       </c>
       <c r="L13" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="M13" t="n">
         <v>11109</v>
       </c>
       <c r="N13" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O13"/>
       <c r="P13"/>
@@ -18085,7 +18392,7 @@
       <c r="U13"/>
       <c r="V13"/>
       <c r="W13" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X13"/>
     </row>
@@ -18094,22 +18401,22 @@
         <v>480</v>
       </c>
       <c r="B14" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C14" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="D14" t="s">
         <v>461</v>
       </c>
       <c r="E14" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="F14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G14" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H14" t="n" s="5">
         <v>45869</v>
@@ -18124,13 +18431,13 @@
         <v>15400</v>
       </c>
       <c r="L14" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="M14" t="n">
         <v>11109</v>
       </c>
       <c r="N14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O14"/>
       <c r="P14"/>
@@ -18141,7 +18448,7 @@
       <c r="U14"/>
       <c r="V14"/>
       <c r="W14" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X14"/>
     </row>
@@ -18150,22 +18457,22 @@
         <v>482</v>
       </c>
       <c r="B15" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="C15" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="D15" t="s">
         <v>484</v>
       </c>
       <c r="E15" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="F15" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G15" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H15" t="n" s="5">
         <v>46035</v>
@@ -18180,13 +18487,13 @@
         <v>59928</v>
       </c>
       <c r="L15" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M15" t="n">
         <v>11109</v>
       </c>
       <c r="N15" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O15"/>
       <c r="P15"/>
@@ -18197,7 +18504,7 @@
       <c r="U15"/>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X15"/>
     </row>
@@ -18206,22 +18513,22 @@
         <v>485</v>
       </c>
       <c r="B16" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="C16" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="D16" t="s">
         <v>487</v>
       </c>
       <c r="E16" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="F16" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G16" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H16" t="n" s="5">
         <v>45953</v>
@@ -18236,13 +18543,13 @@
         <v>66000</v>
       </c>
       <c r="L16" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M16" t="n">
         <v>11109</v>
       </c>
       <c r="N16" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O16"/>
       <c r="P16"/>
@@ -18253,7 +18560,7 @@
       <c r="U16"/>
       <c r="V16"/>
       <c r="W16" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X16"/>
     </row>
@@ -18262,22 +18569,22 @@
         <v>488</v>
       </c>
       <c r="B17" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C17" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D17" t="s">
         <v>490</v>
       </c>
       <c r="E17" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="F17" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G17" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="H17" t="n" s="5">
         <v>45947</v>
@@ -18292,13 +18599,13 @@
         <v>78000</v>
       </c>
       <c r="L17" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M17" t="n">
         <v>11109</v>
       </c>
       <c r="N17" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O17"/>
       <c r="P17"/>
@@ -18309,7 +18616,7 @@
       <c r="U17"/>
       <c r="V17"/>
       <c r="W17" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X17"/>
     </row>
@@ -18318,22 +18625,22 @@
         <v>495</v>
       </c>
       <c r="B18" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C18" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D18" t="s">
         <v>497</v>
       </c>
       <c r="E18" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="F18" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G18" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H18" t="n" s="5">
         <v>45975</v>
@@ -18348,13 +18655,13 @@
         <v>66000</v>
       </c>
       <c r="L18" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M18" t="n">
         <v>11109</v>
       </c>
       <c r="N18" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O18"/>
       <c r="P18"/>
@@ -18365,7 +18672,7 @@
       <c r="U18"/>
       <c r="V18"/>
       <c r="W18" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X18"/>
     </row>
@@ -18374,22 +18681,22 @@
         <v>498</v>
       </c>
       <c r="B19" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="C19" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="D19" t="s">
         <v>461</v>
       </c>
       <c r="E19" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="F19" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G19" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H19" t="n" s="5">
         <v>45940</v>
@@ -18404,13 +18711,13 @@
         <v>42000</v>
       </c>
       <c r="L19" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M19" t="n">
         <v>11109</v>
       </c>
       <c r="N19" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O19"/>
       <c r="P19"/>
@@ -18421,7 +18728,7 @@
       <c r="U19"/>
       <c r="V19"/>
       <c r="W19" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X19"/>
     </row>
@@ -18430,22 +18737,22 @@
         <v>499</v>
       </c>
       <c r="B20" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C20" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D20" t="s">
         <v>501</v>
       </c>
       <c r="E20" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="F20" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G20" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H20" t="n" s="5">
         <v>46045</v>
@@ -18460,13 +18767,13 @@
         <v>59928</v>
       </c>
       <c r="L20" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M20" t="n">
         <v>11109</v>
       </c>
       <c r="N20" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="O20"/>
       <c r="P20"/>
@@ -18477,7 +18784,7 @@
       <c r="U20"/>
       <c r="V20"/>
       <c r="W20" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="X20"/>
     </row>
@@ -18565,16 +18872,16 @@
         <v>276</v>
       </c>
       <c r="B2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="D2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="E2" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F2" t="n" s="3">
         <v>89586</v>
@@ -18627,16 +18934,16 @@
         <v>342</v>
       </c>
       <c r="B3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C3" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D3" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="E3" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F3" t="n" s="3">
         <v>894900</v>
@@ -18689,16 +18996,16 @@
         <v>342</v>
       </c>
       <c r="B4" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D4" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="E4" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F4" t="n" s="3">
         <v>968774</v>
@@ -18751,16 +19058,16 @@
         <v>342</v>
       </c>
       <c r="B5" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C5" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D5" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="E5" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n" s="3">
         <v>1237244</v>
@@ -18813,16 +19120,16 @@
         <v>436</v>
       </c>
       <c r="B6" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C6" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D6" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E6" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F6" t="n" s="3">
         <v>2715200</v>
@@ -18875,16 +19182,16 @@
         <v>436</v>
       </c>
       <c r="B7" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C7" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D7" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="E7" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F7" t="n" s="3">
         <v>2715200</v>
@@ -18937,16 +19244,16 @@
         <v>488</v>
       </c>
       <c r="B8" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C8" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D8" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="E8" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F8" t="n" s="3">
         <v>78000</v>
@@ -18961,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n" s="3">
-        <v>65000</v>
+        <v>19500</v>
       </c>
       <c r="K8" t="n" s="3">
-        <v>65000</v>
+        <v>19500</v>
       </c>
       <c r="L8" t="n" s="3">
         <v>0</v>
@@ -18973,10 +19280,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n" s="3">
-        <v>143000</v>
+        <v>97500</v>
       </c>
       <c r="O8" t="n" s="3">
-        <v>143000</v>
+        <v>97500</v>
       </c>
       <c r="P8" t="n" s="3">
         <v>0</v>
@@ -18985,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n" s="5">
-        <v>46295</v>
+        <v>46314</v>
       </c>
       <c r="S8" t="n" s="5">
         <v>46347</v>
@@ -19060,10 +19367,10 @@
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G2" t="n" s="3">
         <v>89586</v>
@@ -19091,13 +19398,13 @@
         <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="E3" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G3" t="n" s="3">
         <v>89586</v>
@@ -19130,10 +19437,10 @@
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F4" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G4" t="n" s="3">
         <v>894900</v>
@@ -19161,13 +19468,13 @@
         <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E5" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F5" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G5" t="n" s="3">
         <v>894900</v>
@@ -19199,13 +19506,13 @@
         <v>232</v>
       </c>
       <c r="D6" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="E6" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F6" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G6" t="n" s="3">
         <v>1855262</v>
@@ -19237,13 +19544,13 @@
         <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="E7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F7" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G7" t="n" s="3">
         <v>2392202</v>
@@ -19276,10 +19583,10 @@
       </c>
       <c r="D8"/>
       <c r="E8" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="F8" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G8" t="n" s="3">
         <v>8890403.41</v>
@@ -19308,10 +19615,10 @@
       </c>
       <c r="D9"/>
       <c r="E9" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="F9" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G9" t="n" s="3">
         <v>10762356.94</v>
@@ -19340,10 +19647,10 @@
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F10" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G10" t="n" s="3">
         <v>2715200</v>
@@ -19371,13 +19678,13 @@
         <v>232</v>
       </c>
       <c r="D11" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="E11" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F11" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G11" t="n" s="3">
         <v>2715200</v>
@@ -19409,13 +19716,13 @@
         <v>232</v>
       </c>
       <c r="D12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E12" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F12" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G12" t="n" s="3">
         <v>2715200</v>
@@ -19448,10 +19755,10 @@
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F13" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G13" t="n" s="3">
         <v>16228968.43</v>
@@ -19480,10 +19787,10 @@
       </c>
       <c r="D14"/>
       <c r="E14" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G14" t="n" s="3">
         <v>23100</v>
@@ -19512,10 +19819,10 @@
       </c>
       <c r="D15"/>
       <c r="E15" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="F15" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G15" t="n" s="3">
         <v>52800</v>
@@ -19544,10 +19851,10 @@
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="F16" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G16" t="n" s="3">
         <v>32500</v>
@@ -19576,10 +19883,10 @@
       </c>
       <c r="D17"/>
       <c r="E17" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="F17" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G17" t="n" s="3">
         <v>20000</v>
@@ -19608,10 +19915,10 @@
       </c>
       <c r="D18"/>
       <c r="E18" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="F18" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G18" t="n" s="3">
         <v>15400</v>
@@ -19640,10 +19947,10 @@
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="F19" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G19" t="n" s="3">
         <v>15400</v>
@@ -19672,10 +19979,10 @@
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="F20" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G20" t="n" s="3">
         <v>15400</v>
@@ -19704,10 +20011,10 @@
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="F21" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G21" t="n" s="3">
         <v>59928</v>
@@ -19736,10 +20043,10 @@
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="F22" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G22" t="n" s="3">
         <v>66000</v>
@@ -19768,10 +20075,10 @@
       </c>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G23" t="n" s="3">
         <v>78000</v>
@@ -19799,13 +20106,13 @@
         <v>232</v>
       </c>
       <c r="D24" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="E24" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="F24" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G24" t="n" s="3">
         <v>78000</v>
@@ -19814,16 +20121,16 @@
         <v>78000</v>
       </c>
       <c r="I24" t="n" s="3">
-        <v>65000</v>
+        <v>19500</v>
       </c>
       <c r="J24" t="n" s="3">
-        <v>65000</v>
+        <v>19500</v>
       </c>
       <c r="K24" t="n" s="3">
-        <v>143000</v>
+        <v>97500</v>
       </c>
       <c r="L24" t="n" s="3">
-        <v>143000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -19838,10 +20145,10 @@
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="F25" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G25" t="n" s="3">
         <v>66000</v>
@@ -19870,10 +20177,10 @@
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="F26" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G26" t="n" s="3">
         <v>42000</v>
@@ -19902,10 +20209,10 @@
       </c>
       <c r="D27"/>
       <c r="E27" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="F27" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G27" t="n" s="3">
         <v>59928</v>
@@ -19982,11 +20289,11 @@
         <v>426</v>
       </c>
       <c r="C2" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -19999,10 +20306,10 @@
         <v>8890403.41</v>
       </c>
       <c r="J2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="K2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -20013,11 +20320,11 @@
         <v>426</v>
       </c>
       <c r="C3" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -20030,10 +20337,10 @@
         <v>10762356.94</v>
       </c>
       <c r="J3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="K3" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -20099,17 +20406,17 @@
         <v>426</v>
       </c>
       <c r="C2" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="F2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="H2" t="n" s="3">
         <v>444520.17</v>
@@ -20124,7 +20431,7 @@
         <v>444520.17</v>
       </c>
       <c r="L2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -20135,17 +20442,17 @@
         <v>450</v>
       </c>
       <c r="C3" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F3" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="H3" t="n" s="3">
         <v>811450</v>
@@ -20160,7 +20467,7 @@
         <v>811450</v>
       </c>
       <c r="L3" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -20206,10 +20513,10 @@
         <v>45708</v>
       </c>
       <c r="D2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="E2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
